--- a/cache/peyk.xlsx
+++ b/cache/peyk.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AFBBB7-1999-411A-835B-6B7D3A3904BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39FCF10-9C8C-42F1-8CD6-D4920ADF02CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>واسط تفصيلي واسط</t>
   </si>
@@ -36,15 +36,6 @@
     <t>157</t>
   </si>
   <si>
-    <t>70800</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>10022</t>
-  </si>
-  <si>
     <t>86</t>
   </si>
   <si>
@@ -63,57 +54,21 @@
     <t>10072</t>
   </si>
   <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>10074</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>10070</t>
-  </si>
-  <si>
     <t>نام</t>
   </si>
   <si>
     <t>کد فودسافت</t>
   </si>
   <si>
-    <t>مجيد عربيان</t>
-  </si>
-  <si>
-    <t>كامران شريفي</t>
-  </si>
-  <si>
     <t>شهرام محمدي</t>
   </si>
   <si>
     <t>بهزاد فاضلي</t>
   </si>
   <si>
-    <t>پويا  مستاجران</t>
-  </si>
-  <si>
-    <t>الف پيك</t>
-  </si>
-  <si>
-    <t>پیک متفرقه پیک</t>
-  </si>
-  <si>
-    <t>حافظ زمانی</t>
-  </si>
-  <si>
-    <t>جواد زمانی</t>
-  </si>
-  <si>
     <t>134</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>82</t>
   </si>
   <si>
@@ -123,20 +78,74 @@
     <t>81</t>
   </si>
   <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
     <t>واسط واسط</t>
+  </si>
+  <si>
+    <t>پويا مستاجران</t>
+  </si>
+  <si>
+    <t>جواد زماني</t>
+  </si>
+  <si>
+    <t>حافظ زماني</t>
+  </si>
+  <si>
+    <t>سجاد شيراني</t>
+  </si>
+  <si>
+    <t>پيک متفرقه (بيرون بر)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10077</t>
+  </si>
+  <si>
+    <t>10078</t>
+  </si>
+  <si>
+    <t>10128</t>
+  </si>
+  <si>
+    <t>10127</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>147</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +156,12 @@
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -181,10 +196,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,151 +483,158 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="58.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>